--- a/human_validation/judge/kor/judge_D020_S001_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D020_S001_P002__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,145 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 [이름] 선생님입니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제 작업을 프리랜서 사업으로 만들어보려고 하고 있는데, 생각보다 저를 많이 힘들게 하고 있어서 왔어요. 인보이스나 클라이언트 메시지 때문에 진짜 긴장하게 되고, 그러면 그걸 처리하는 걸 피하게 돼요. 가끔은 부엌 식탁에서 울고 있기도 하고, 고지서 내는 것 같은 평범한 일도 깜빡해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 걱정, 눈물, 건망증을 처음 느끼기 시작하신 게 언제인가요? 프리랜서 사업을 시작하신 시기쯤부터였나요, 그리고 그 이후로 얼마나 계속되고 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네, 한 달 전쯤 제 작업을 좀 더 정식 프리랜서 사업으로 만들려고 시작했을 때부터예요. 그 이후로 계속 그래요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 지난 한 달 동안, 사업 관련 일을 다루지 않을 때조차도 대부분의 날에 기분이 가라앉거나 슬프거나, 예전에 즐기시던 것들에 흥미가 없다고 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 잘 모르겠어요. 사업 관련 일 말고 다른 데서도 항상 그런 건 딱히 못 느꼈어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 프리랜서 사업에 대한 걱정 말고, 건강이나 인간관계, 다른 책임들처럼 삶의 다른 부분에 대해서도 지나치게 걱정하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 아니요, 그런 것 같지는 않아요. 대부분 프리랜서 사업이랑 거기서 딸려오는 것들에 집중돼 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 걱정과 눈물 외에, 불안한 감정과는 별개로 이 사업 상황에 대해 특히 지속적으로 기분이 가라앉거나 절망적이거나 우울하다고 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네, 가끔은 꽤 우울해지기도 해요. 인보이스나 클라이언트 메시지 때문에 너무 긴장해서 그냥 피해버리게 되고, 그러다 결국 부엌 식탁에서 울게 돼요. 평범한 사업 일들도 제가 감당을 못 하는 것 같은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 이 스트레스가 인간관계나 수면, 사업 외적인 일상적 책임을 처리하는 능력 같은 삶의 다른 영역에도 영향을 주고 있나요, 아니면 사업 관련 일에만 국한되어 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 조금씩 번지기 시작했어요. 클라이언트한테 답장하는 걸 미루게 됐고, 전시 준비랑 다른 일들을 따라가려다 공과금 내는 것도 놓쳤어요. 집안일도 제대로 챙기기가 더 힘들어졌어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 적응장애 (D020) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>진단명: 적응장애 (D020)
 인구통계: 성별 여성 / 나이 32 / 직업상태 not in workforce / 최종학력 전문학사
@@ -575,194 +705,29 @@
 증상 지속 기간: 1 month
 추가 요건: Symptoms must develop within 3 months of the onset of the stressor, Within 6 months of the termination of the stressor or its consequences
 주호소 증상 코드: S081
-배경 서술: 길다는 소규모지만 공개적인 지역사회 예술 계약을 제안받은 뒤, 비공식적인 아트 팝업과 정원에서 영감을 받은 스케치 작업에서 좀 더 정식 프리랜서 비주얼 스토리텔링 사업으로 방향을 바꾸기로 결정했다. 이 변화에는 인보이스 발행, 클라이언트 수정 요청 대응, 마케팅 게시물, 고정된 납품 일정이 요구되었고, 이는 예전에 그녀의 작업을 지속 가능하게 느끼게 해주었던 여유로운 작업 방식과 충돌했다. 그 후 한 달 동안 그녀의 스트레스 반응은 기본적인 업무 처리에까지 지장을 주기 시작했다. 클라이언트와의 소통을 미뤘고, 팝업 전시를 준비하느라 공과금 납부를 놓쳤으며, 창작 루틴을 유지하기가 점점 더 힘들어졌다. 그래도 그 계약을 계속 유지하고 싶다는 마음이 있었고 이런 패턴을 일찍 알아차렸기에, 그녀는 애크워스의 한 예술 비영리단체가 추천해 준 이용료 조정형 상담 클리닉에 연락했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 [이름] 선생님입니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제 작업을 프리랜서 사업으로 만들어보려고 하고 있는데, 생각보다 저를 많이 힘들게 하고 있어서 왔어요. 인보이스나 클라이언트 메시지 때문에 진짜 긴장하게 되고, 그러면 그걸 처리하는 걸 피하게 돼요. 가끔은 부엌 식탁에서 울고 있기도 하고, 고지서 내는 것 같은 평범한 일도 깜빡해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 걱정, 눈물, 건망증을 처음 느끼기 시작하신 게 언제인가요? 프리랜서 사업을 시작하신 시기쯤부터였나요, 그리고 그 이후로 얼마나 계속되고 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네, 한 달 전쯤 제 작업을 좀 더 정식 프리랜서 사업으로 만들려고 시작했을 때부터예요. 그 이후로 계속 그래요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 지난 한 달 동안, 사업 관련 일을 다루지 않을 때조차도 대부분의 날에 기분이 가라앉거나 슬프거나, 예전에 즐기시던 것들에 흥미가 없다고 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 잘 모르겠어요. 사업 관련 일 말고 다른 데서도 항상 그런 건 딱히 못 느꼈어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 프리랜서 사업에 대한 걱정 말고, 건강이나 인간관계, 다른 책임들처럼 삶의 다른 부분에 대해서도 지나치게 걱정하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 아니요, 그런 것 같지는 않아요. 대부분 프리랜서 사업이랑 거기서 딸려오는 것들에 집중돼 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 걱정과 눈물 외에, 불안한 감정과는 별개로 이 사업 상황에 대해 특히 지속적으로 기분이 가라앉거나 절망적이거나 우울하다고 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네, 가끔은 꽤 우울해지기도 해요. 인보이스나 클라이언트 메시지 때문에 너무 긴장해서 그냥 피해버리게 되고, 그러다 결국 부엌 식탁에서 울게 돼요. 평범한 사업 일들도 제가 감당을 못 하는 것 같은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 이 스트레스가 인간관계나 수면, 사업 외적인 일상적 책임을 처리하는 능력 같은 삶의 다른 영역에도 영향을 주고 있나요, 아니면 사업 관련 일에만 국한되어 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 조금씩 번지기 시작했어요. 클라이언트한테 답장하는 걸 미루게 됐고, 전시 준비랑 다른 일들을 따라가려다 공과금 내는 것도 놓쳤어요. 집안일도 제대로 챙기기가 더 힘들어졌어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
+배경 서술: 길다는 소규모지만 공개적인 지역사회 예술 계약을 제안받은 뒤, 비공식적인 아트 팝업과 정원에서 영감을 받은 스케치 작업에서 좀 더 정식 프리랜서 비주얼 스토리텔링 사업으로 방향을 바꾸기로 결정했다. 이 변화에는 인보이스 발행, 클라이언트 수정 요청 대응, 마케팅 게시물, 고정된 납품 일정이 요구되었고, 이는 예전에 그녀의 작업을 지속 가능하게 느끼게 해주었던 여유로운 작업 방식과 충돌했다. 그 후 한 달 동안 그녀의 스트레스 반응은 기본적인 업무 처리에까지 지장을 주기 시작했다. 클라이언트와의 소통을 미뤘고, 팝업 전시를 준비하느라 공과금 납부를 놓쳤으며, 창작 루틴을 유지하기가 점점 더 힘들어졌다. 그래도 그 계약을 계속 유지하고 싶다는 마음이 있었고 이런 패턴을 일찍 알아차렸기에, 그녀는 애크워스의 한 예술 비영리단체가 추천해 준 이용료 조정형 상담 클리닉에 연락했다.
+표집된 증상 목록:
+  - S081 스트레스 관련 부적응 반응: 확인 가능한 스트레스 요인에 대한 반응으로 나타나는 정서적·행동적 증상.</t>
+        </is>
+      </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003); 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 적응장애 (D020, ICD: F43.23)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: adjustment_symptoms (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
-  확인된 근거: 스트레스 관련 부적응 반응: 확인 가능한 스트레스 요인에 대한 반응으로 나타나는 정서적·행동적 증상.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 적응장애 (D020, ICD: F43.23)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: 0.5
+체크리스트 그룹: adjustment_symptoms (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
+확인된 근거:
+  - 스트레스 관련 부적응 반응: 확인 가능한 스트레스 요인에 대한 반응으로 나타나는 정서적·행동적 증상.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D020_S001_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D020_S001_P002__claude-sonnet-5_kor.xlsx
@@ -691,6 +691,11 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -723,11 +728,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D020_S001_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D020_S001_P002__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1434</v>
+        <v>0.7083</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.9167</v>
+        <v>0.7083</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1712</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.2167</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.875</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
